--- a/artfynd/A 45301-2023 artfynd.xlsx
+++ b/artfynd/A 45301-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 45301-2023 artfynd.xlsx
+++ b/artfynd/A 45301-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3004436</v>
+        <v>79569710</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ramsebo, Sm</t>
+          <t>Ramsebo, 750 m SSV fyrvägskorsningen, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>537973.6045725184</v>
+        <v>538008</v>
       </c>
       <c r="R2" t="n">
-        <v>6348533.267041814</v>
+        <v>6348574</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,27 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1999-05-31</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1999-05-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Häll- och mossrikt gammal barrskog på minst 5 ställen</t>
+          <t>2019-08-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,26 +758,362 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granlåga i blockrik granskogssluttning</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>79569757</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96426</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2671</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fällmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Antitrichia curtipendula</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ramsebo, 750 m SSV fyrvägskorsningen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>538008</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6348574</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Blockrik granskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>79569699</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ramsebo, 750 m SSV fyrvägskorsningen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>538008</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6348574</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2019-08-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granlåga i blockrik granskogssluttning</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tommy Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3004436</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ramsebo, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>537974</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6348533</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Hultsfred</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Virserum</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>1999-05-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>1999-05-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Häll- och mossrikt gammal barrskog på minst 5 ställen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Jörg Adelmann</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Jörg Adelmann</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45301-2023 artfynd.xlsx
+++ b/artfynd/A 45301-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79569710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79569757</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79569699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,8 +1134,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3004436</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>